--- a/Аналитический отчёт.xlsx
+++ b/Аналитический отчёт.xlsx
@@ -4,19 +4,23 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="730" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Весь отдел" sheetId="3" r:id="rId1"/>
     <sheet name="Менеджеры за год" sheetId="2" r:id="rId2"/>
     <sheet name="Менеджеры по месяцам" sheetId="1" r:id="rId3"/>
+    <sheet name="Коэф.пролонг., визуал." sheetId="4" r:id="rId4"/>
+    <sheet name="Эффектив. в 1 месяц, визуал." sheetId="5" r:id="rId5"/>
+    <sheet name="Эффектив. во 2 месяц, визуал." sheetId="6" r:id="rId6"/>
+    <sheet name="Процент проектов, визуал." sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="35">
   <si>
     <t>Январь 2023</t>
   </si>
@@ -109,6 +113,24 @@
   </si>
   <si>
     <t>коэффициент</t>
+  </si>
+  <si>
+    <t>При сравнении работы менеджеров на основании заложенных в компании коэффициентов пролонгации самым активным менеджером является Васильев А.А. - особенно эффективными для него был период с Марта по Май, Июль-Август и Ноябрь 2023 года, но менеджер совсем не занимался теми проектами, которые по каким-либо причинам не пролонгировал в 1-ый месяц, потому что 2-ой коэффициент почти не выделяется.
+Следующим следует отметить менеджера Михайлова А.С., который особенно эффективно поработал в Феврале 2023 (причём этот показатель является самым успешным по всему отделу за весь год), а также в Мае и Июле 2023.
+Далее следует отметить менеджера Соколову А.В., Смирнову О.В. и Кузнецова М.И., работу которых можно значимо выделить на тепловой карте. Причём Кузнецов М.И., помимо 1-го месяца, показал очень высокий результат во 2-ой пролонгации в Марте 2023. Кроме того во 2-ом коэффициенте пролонгации можно отметить Смирнову О.В., и в Январе 2023 выделилась Иванова М.С.</t>
+  </si>
+  <si>
+    <t>Если в первом выводе на тепловой карте оценка шла по суммам отгрузки, и, например, один более выгодный проект будучи пролонгированным мог дать бОльший визуальный эффект, чем 10 проектов подешевле, то на данной диаграмме за весь год сразу можно оценить работу менеджеров по количеству проектов, которые надо было пролонгировать (весь столбик), сколько из них менеджер пролонгировал (синяя часть столбика), и сколько не пролонгировал (красная часть столбика).
+Наглядно видно, что у за весь год по 1-ой пролонгации больше всего проектов проработал Васильев А.А., затем Соколова А.В., и замыкает тройку лидеров Смирнова О.В.
+Михайлов А.С. по количеству пролонгированных проектов на 4-ом месте, но, опирясь на тепловую карту, можно предположить, что все эти проекты были проработаны в Феврале 2023.</t>
+  </si>
+  <si>
+    <t>Как и в предыдущей диаграмме оцениваем годовое количество пролонгированных проектов, но уже во 2-ой месяц. С незначительным отрывом больше всех пролонгировала Смирнова О.В., а Попова Е.Н., Васильев А.А., Кузнецов М.И. и Иванова М.С. показали равные между собой вторые результаты. Следует отметить, что Михайлов А.С. не пролонгировал ни одного проекта во 2-ой месяц.
+Вместе с тем, менеджеры Федорова М.В. и Петрова А.Д. согласно всем проанализированным графикам пролонгировали все возложенные на них проекты, не имея за собой "хвостов" на 2-ой месяц, но количество этих пролонгированных проектов очень мало.</t>
+  </si>
+  <si>
+    <t>В предыдущих столбчатых диаграммах заметно большое количество красных проектов (т.е. которые не пролонгированы), поэтому логично оценить нагрузку на каждого менеджера с помощью круговой диаграммы. И на ней видно, что 29,9% проектов (почти треть всех проектов!) приходится только на одного  Васильева А.А.
+Примерно одинаковое количество проектов приходится на Соколову А.В. (16,4%), Смирнову О.В. (14,5%) и на Иванову М.С. и Попову Е.Н. (по 12,6%). Меньшее количество приходится на Михайлова А.С. (8,41%) и в два раза меньше на Кузнецову М.И. (4,21%). Петрова А.Д. и Федорова М.В. по нагрузке имеют совершенно незначительные проценты.</t>
   </si>
 </sst>
 </file>
@@ -205,15 +227,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -229,6 +245,21 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -241,6 +272,202 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>124267</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="104775" y="1562100"/>
+          <a:ext cx="10058400" cy="4467667"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="152400" y="1524000"/>
+          <a:ext cx="7620000" cy="3810000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="1057275"/>
+          <a:ext cx="7620000" cy="3810000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="304800" y="1295400"/>
+          <a:ext cx="7143750" cy="4286250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -543,314 +770,314 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4">
         <v>47</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>11</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>11</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="4">
         <v>3</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="4">
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>7</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>2</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>36</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>1</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>16</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>5</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>5</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>2</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>20</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>9</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>11</v>
       </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
         <v>0.01</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>14</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>6</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>11</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>1</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>13</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>2</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>8</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>1</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>16</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>5</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>11</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>1</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="4">
         <v>1.6E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>12</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>4</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>11</v>
       </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>15</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>7</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <v>8</v>
       </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>20</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>4</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>2.7E-2</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>8</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="4">
         <v>1</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>12</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>4</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>4.7E-2</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>16</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="4">
         <v>1</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="4">
         <v>2E-3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>22</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>7</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>3.9E-2</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="4">
         <v>8</v>
       </c>
-      <c r="F14" s="6">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
         <v>0.01</v>
       </c>
     </row>
@@ -879,268 +1106,268 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="8"/>
+      <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
         <v>64</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>20</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>0.129</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>45</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="4">
         <v>2</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="4">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>27</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>2</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>0.01</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>26</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>2</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>1.9E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>9</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>5</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>3</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>2</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <v>3.1E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>18</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>7</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>7.8E-2</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>11</v>
       </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>27</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>4</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>23</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>2</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>31</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>11</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>16</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>3</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>35</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>15</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>19</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="4">
         <v>1</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="4">
         <v>2E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>1</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>1</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>1</v>
       </c>
-      <c r="C12" s="6">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
         <v>1</v>
       </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1179,470 +1406,470 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>0.06</v>
       </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
         <v>0.20799999999999999</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>0.32100000000000001</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>0.249</v>
       </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
         <v>0.13600000000000001</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>0.223</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <v>0.08</v>
       </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6">
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
         <v>0.23100000000000001</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="4">
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="C5" s="6">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
         <v>0.121</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="4">
         <v>0.104</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>0.35899999999999999</v>
       </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>0.183</v>
       </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
         <v>0.20399999999999999</v>
       </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="4">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
         <v>0.108</v>
       </c>
-      <c r="H10" s="6">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="4">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="L10" s="6">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
+      <c r="L10" s="4">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4">
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>5.5E-2</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>0.152</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="4">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6">
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="4">
         <v>0.159</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="4">
         <v>0.122</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="4">
         <v>0.129</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="6">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6">
+      <c r="B12" s="4">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="6">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6">
+      <c r="B13" s="4">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1652,470 +1879,470 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="A17" s="8"/>
+      <c r="B17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="6">
-        <v>0</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="B18" s="4">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="D18" s="6">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="F18" s="6">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6">
-        <v>0</v>
-      </c>
-      <c r="I18" s="6">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6">
-        <v>0</v>
-      </c>
-      <c r="K18" s="6">
-        <v>0</v>
-      </c>
-      <c r="L18" s="6">
-        <v>0</v>
-      </c>
-      <c r="M18" s="6">
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="4">
         <v>0.184</v>
       </c>
-      <c r="C19" s="6">
-        <v>0</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6">
+      <c r="C19" s="4">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="H19" s="6">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6">
-        <v>0</v>
-      </c>
-      <c r="K19" s="6">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6">
+      <c r="H19" s="4">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="6">
-        <v>0</v>
-      </c>
-      <c r="C20" s="6">
+      <c r="B20" s="4">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="4">
         <v>0.34599999999999997</v>
       </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6">
-        <v>0</v>
-      </c>
-      <c r="I20" s="6">
-        <v>0</v>
-      </c>
-      <c r="J20" s="6">
-        <v>0</v>
-      </c>
-      <c r="K20" s="6">
-        <v>0</v>
-      </c>
-      <c r="L20" s="6">
-        <v>0</v>
-      </c>
-      <c r="M20" s="6">
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="6">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6">
-        <v>0</v>
-      </c>
-      <c r="L21" s="6">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6">
+      <c r="B21" s="4">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="6">
-        <v>0</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6">
-        <v>0</v>
-      </c>
-      <c r="J22" s="6">
-        <v>0</v>
-      </c>
-      <c r="K22" s="6">
-        <v>0</v>
-      </c>
-      <c r="L22" s="6">
-        <v>0</v>
-      </c>
-      <c r="M22" s="6">
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="6">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
+      <c r="B23" s="4">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6">
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6">
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="6">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6">
+      <c r="B24" s="4">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
         <v>0.16500000000000001</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="4">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="J24" s="6">
-        <v>0</v>
-      </c>
-      <c r="K24" s="6">
-        <v>0</v>
-      </c>
-      <c r="L24" s="6">
-        <v>0</v>
-      </c>
-      <c r="M24" s="6">
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4">
         <v>0.104</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="6">
-        <v>0</v>
-      </c>
-      <c r="C25" s="6">
+      <c r="B25" s="4">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="D25" s="6">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6">
-        <v>0</v>
-      </c>
-      <c r="K25" s="6">
-        <v>0</v>
-      </c>
-      <c r="L25" s="6">
-        <v>0</v>
-      </c>
-      <c r="M25" s="6">
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="6">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6">
-        <v>0</v>
-      </c>
-      <c r="K26" s="6">
-        <v>0</v>
-      </c>
-      <c r="L26" s="6">
-        <v>0</v>
-      </c>
-      <c r="M26" s="6">
+      <c r="B26" s="4">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="6">
-        <v>0</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0</v>
-      </c>
-      <c r="D27" s="6">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6">
-        <v>0</v>
-      </c>
-      <c r="K27" s="6">
-        <v>0</v>
-      </c>
-      <c r="L27" s="6">
-        <v>0</v>
-      </c>
-      <c r="M27" s="6">
+      <c r="B27" s="4">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2128,4 +2355,625 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>